--- a/code/Table_aim2_secondary.xlsx
+++ b/code/Table_aim2_secondary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA8"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -435,7 +435,7 @@
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="48" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -444,17 +444,19 @@
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="21" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="22" customWidth="1" min="20" max="20"/>
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="21" customWidth="1" min="22" max="22"/>
-    <col width="20" customWidth="1" min="23" max="23"/>
-    <col width="18" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="21" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
     <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="32" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -570,25 +572,35 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>welch_p_value</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>model_family_p</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>q_fdr</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>effect_direction</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>source_column</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -641,60 +653,63 @@
         <v>28</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1300873374734078</v>
+        <v>1.483193421444162</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08817329002033837</v>
+        <v>0.1524771781316907</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09856125657661254</v>
+        <v>1.39820636722879</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05640396151733591</v>
+        <v>0.2064492702701683</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03152608089679527</v>
+        <v>0.08498705421537256</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4353656622096378</v>
+        <v>0.4614252999197991</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1495200746536932</v>
+        <v>-0.06400202764473212</v>
       </c>
       <c r="R2" t="n">
-        <v>1.004943824017964</v>
+        <v>0.9722754614838974</v>
       </c>
       <c r="S2" t="n">
         <v>5000</v>
       </c>
       <c r="T2" t="n">
-        <v>1.483445301774754</v>
+        <v>1.688623307581887</v>
       </c>
       <c r="U2" t="n">
-        <v>35.96466015948098</v>
+        <v>48.51142280322171</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1466675369782948</v>
+        <v>0.09771068060853218</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3422242529493546</v>
-      </c>
-      <c r="X2" t="inlineStr">
+        <v>0.09771068060853218</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.3455954647813743</v>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>higher in SAD</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Neural_Dist_Safety_Background</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>resolved</t>
         </is>
@@ -747,60 +762,63 @@
         <v>28</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1285551021579494</v>
+        <v>1.479823626483557</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09264756978923594</v>
+        <v>0.1942086984353445</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1267838346433344</v>
+        <v>1.558473712815117</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09698240949272487</v>
+        <v>0.1195652140947562</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001771267514614983</v>
+        <v>-0.07865008633156001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01863303336686996</v>
+        <v>-0.4993130805700229</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.513565675083519</v>
+        <v>-0.9740859627007233</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5922022128950996</v>
+        <v>0.02346077765077016</v>
       </c>
       <c r="S3" t="n">
         <v>5000</v>
       </c>
       <c r="T3" t="n">
-        <v>0.06651606431530295</v>
+        <v>-1.696039382747858</v>
       </c>
       <c r="U3" t="n">
-        <v>47.84413069520072</v>
+        <v>35.06238254286284</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9472441508466121</v>
+        <v>0.09874156136610693</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9472441508466121</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>higher in SAD</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+        <v>0.09874156136610693</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.3455954647813743</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>lower in SAD</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Neural_Dist_Threat_Background</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>resolved</t>
         </is>
@@ -853,60 +871,63 @@
         <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1783705426639688</v>
+        <v>1.517341694840898</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1269747265245408</v>
+        <v>0.1198274062129216</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1366094902291264</v>
+        <v>1.519858740961526</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1171885142545761</v>
+        <v>0.1317298784074646</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04176105243484235</v>
+        <v>-0.00251704612062742</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3432047005582242</v>
+        <v>-0.01989374615125264</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1970101615398488</v>
+        <v>-0.6127509058360042</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9713910618300602</v>
+        <v>0.5247360362081663</v>
       </c>
       <c r="S4" t="n">
         <v>5000</v>
       </c>
       <c r="T4" t="n">
-        <v>1.209854869467374</v>
+        <v>-0.07136347141985432</v>
       </c>
       <c r="U4" t="n">
-        <v>45.4332277238017</v>
+        <v>48.45301578991505</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2325921056656618</v>
+        <v>0.9434022332141585</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4070361849149082</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>higher in SAD</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+        <v>0.9434022332141585</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.9434022332141585</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>lower in SAD</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Neural_Dist_Threat_Safety</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>resolved</t>
         </is>
@@ -928,17 +949,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Neural_Certainty_CSS</t>
+          <t>Prototype_Certainty_CSS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CSS certainty</t>
+          <t>Prototype CSS certainty</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2 * |P(safety | CSS) - 0.50|</t>
+          <t>2 * |P_prototype_safety_css - 0.50|</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -948,7 +969,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Higher = less ambiguous CSS evidence</t>
+          <t>Higher = less ambiguous prototype safety evidence for CSS</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -958,60 +979,63 @@
         <v>28</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3831693613119109</v>
+        <v>0.1003852985579937</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2302050957355015</v>
+        <v>0.1198568282036435</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2367544285572005</v>
+        <v>0.1242159169597024</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1741286939539822</v>
+        <v>0.1134075112305132</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1464149327547103</v>
+        <v>-0.02383061840170872</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7275346571421177</v>
+        <v>-0.204823038800574</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1569402358274535</v>
+        <v>-0.8130648587471739</v>
       </c>
       <c r="R5" t="n">
-        <v>1.472045034805979</v>
+        <v>0.3631526495599417</v>
       </c>
       <c r="S5" t="n">
         <v>5000</v>
       </c>
       <c r="T5" t="n">
-        <v>2.515813511388849</v>
+        <v>-0.7238286201361032</v>
       </c>
       <c r="U5" t="n">
-        <v>40.28768443161758</v>
+        <v>45.98970210973896</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01596119618209416</v>
+        <v>0.4728369475107381</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1112580352005434</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>higher in SAD</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+        <v>0.4728369475107381</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.6619717265150333</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>lower in SAD</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Neural_Certainty_CSS</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Prototype_Certainty_CSS</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
         <is>
           <t>resolved</t>
         </is>
@@ -1033,17 +1057,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Neural_Certainty_CSR</t>
+          <t>Prototype_Certainty_CSR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CSR certainty</t>
+          <t>Prototype CSR certainty</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2 * |P(threat | CSR) - 0.50|</t>
+          <t>2 * |P_prototype_threat_csr - 0.50|</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1053,7 +1077,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Higher = less ambiguous CSR evidence</t>
+          <t>Higher = less ambiguous prototype threat evidence for CSR</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -1063,60 +1087,63 @@
         <v>28</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3310221787700166</v>
+        <v>0.6327387902661199</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2176137637339395</v>
+        <v>0.06126300121002913</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2090324688305265</v>
+        <v>0.6489889224798121</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1628462809179963</v>
+        <v>0.04549107177846967</v>
       </c>
       <c r="O6" t="n">
-        <v>0.12198970993949</v>
+        <v>-0.0162501322136922</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6440683005621686</v>
+        <v>-0.30571553273462</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.09126133778588713</v>
+        <v>-0.8554525693680148</v>
       </c>
       <c r="R6" t="n">
-        <v>1.317244525216265</v>
+        <v>0.2614442466989809</v>
       </c>
       <c r="S6" t="n">
         <v>5000</v>
       </c>
       <c r="T6" t="n">
-        <v>2.224974947448372</v>
+        <v>-1.055361038719713</v>
       </c>
       <c r="U6" t="n">
-        <v>39.99865565370761</v>
+        <v>39.79068672076174</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03178801005729812</v>
+        <v>0.2976262368272386</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1112580352005434</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>higher in SAD</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+        <v>0.2976262368272386</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.5814797502674219</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>lower in SAD</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Neural_Certainty_CSR</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Prototype_Certainty_CSR</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
         <is>
           <t>resolved</t>
         </is>
@@ -1204,24 +1231,27 @@
         <v>0.9343969974782784</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9472441508466121</v>
-      </c>
-      <c r="X7" t="inlineStr">
+        <v>0.9343969974782784</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.9434022332141585</v>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>lower in SAD</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Neural_Safety_Trajectory_Slope</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>resolved</t>
         </is>
@@ -1309,24 +1339,27 @@
         <v>0.3322741430099554</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4651838002139375</v>
-      </c>
-      <c r="X8" t="inlineStr">
+        <v>0.3322741430099554</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.5814797502674219</v>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>lower in SAD</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>Neural_Threat_Trajectory_Slope</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resolved</t>
         </is>

--- a/code/Table_aim2_secondary.xlsx
+++ b/code/Table_aim2_secondary.xlsx
@@ -444,13 +444,13 @@
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="22" customWidth="1" min="20" max="20"/>
     <col width="19" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
-    <col width="21" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
     <col width="16" customWidth="1" min="24" max="24"/>
     <col width="20" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
@@ -653,46 +653,46 @@
         <v>28</v>
       </c>
       <c r="K2" t="n">
-        <v>1.483193421444162</v>
+        <v>0.2314684506042999</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1524771781316907</v>
+        <v>0.1533706281069297</v>
       </c>
       <c r="M2" t="n">
-        <v>1.39820636722879</v>
+        <v>0.2074879754890014</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2064492702701683</v>
+        <v>0.1310787385108941</v>
       </c>
       <c r="O2" t="n">
-        <v>0.08498705421537256</v>
+        <v>0.02398047511529852</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4614252999197991</v>
+        <v>0.1694465536944773</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.06400202764473212</v>
+        <v>-0.3961783266510094</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9722754614838974</v>
+        <v>0.7290540536252698</v>
       </c>
       <c r="S2" t="n">
         <v>5000</v>
       </c>
       <c r="T2" t="n">
-        <v>1.688623307581887</v>
+        <v>0.5928157910303914</v>
       </c>
       <c r="U2" t="n">
-        <v>48.51142280322171</v>
+        <v>43.54635217281516</v>
       </c>
       <c r="V2" t="n">
-        <v>0.09771068060853218</v>
+        <v>0.5563707173345738</v>
       </c>
       <c r="W2" t="n">
-        <v>0.09771068060853218</v>
+        <v>0.5563707173345738</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3455954647813743</v>
+        <v>0.6517481117828272</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -762,50 +762,50 @@
         <v>28</v>
       </c>
       <c r="K3" t="n">
-        <v>1.479823626483557</v>
+        <v>0.250406860425123</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1942086984353445</v>
+        <v>0.1177094810781026</v>
       </c>
       <c r="M3" t="n">
-        <v>1.558473712815117</v>
+        <v>0.2302064012448476</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1195652140947562</v>
+        <v>0.1267753928149779</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.07865008633156001</v>
+        <v>0.02020045918027544</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4993130805700229</v>
+        <v>0.1645151819033414</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9740859627007233</v>
+        <v>-0.3872726190506065</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02346077765077016</v>
+        <v>0.7627129097762194</v>
       </c>
       <c r="S3" t="n">
         <v>5000</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.696039382747858</v>
+        <v>0.5889536918794687</v>
       </c>
       <c r="U3" t="n">
-        <v>35.06238254286284</v>
+        <v>48.22395824619176</v>
       </c>
       <c r="V3" t="n">
-        <v>0.09874156136610693</v>
+        <v>0.5586412386709947</v>
       </c>
       <c r="W3" t="n">
-        <v>0.09874156136610693</v>
+        <v>0.5586412386709947</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3455954647813743</v>
+        <v>0.6517481117828272</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>lower in SAD</t>
+          <t>higher in SAD</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,50 +871,50 @@
         <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>1.517341694840898</v>
+        <v>0.2991152799714809</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1198274062129216</v>
+        <v>0.1760392869776785</v>
       </c>
       <c r="M4" t="n">
-        <v>1.519858740961526</v>
+        <v>0.239382628137274</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1317298784074646</v>
+        <v>0.1424927437816819</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.00251704612062742</v>
+        <v>0.05973265183420687</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.01989374615125264</v>
+        <v>0.3770154856650065</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.6127509058360042</v>
+        <v>-0.1819640990020789</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5247360362081663</v>
+        <v>0.9446261346784078</v>
       </c>
       <c r="S4" t="n">
         <v>5000</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.07136347141985432</v>
+        <v>1.31208218114335</v>
       </c>
       <c r="U4" t="n">
-        <v>48.45301578991505</v>
+        <v>42.11345390330619</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9434022332141585</v>
+        <v>0.1965995474682463</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9434022332141585</v>
+        <v>0.1965995474682463</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.9434022332141585</v>
+        <v>0.6517481117828272</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>lower in SAD</t>
+          <t>higher in SAD</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,7 +1018,7 @@
         <v>0.4728369475107381</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6619717265150333</v>
+        <v>0.6517481117828272</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>0.2976262368272386</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5814797502674219</v>
+        <v>0.6517481117828272</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>0.9343969974782784</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.9434022332141585</v>
+        <v>0.9343969974782784</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>0.3322741430099554</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5814797502674219</v>
+        <v>0.6517481117828272</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>

--- a/code/Table_aim2_secondary.xlsx
+++ b/code/Table_aim2_secondary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -435,7 +435,7 @@
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="48" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="47" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -444,19 +444,17 @@
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="22" customWidth="1" min="20" max="20"/>
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="21" customWidth="1" min="22" max="22"/>
-    <col width="21" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="10" customWidth="1" min="27" max="27"/>
-    <col width="32" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -572,35 +570,25 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>welch_p_value</t>
+          <t>q_fdr</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>model_family_p</t>
+          <t>effect_direction</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>q_fdr</t>
+          <t>status</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>effect_direction</t>
+          <t>source_column</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>source_column</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -653,63 +641,60 @@
         <v>28</v>
       </c>
       <c r="K2" t="n">
-        <v>1.483193421444162</v>
+        <v>0.1300873374734078</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1524771781316907</v>
+        <v>0.08817329002033837</v>
       </c>
       <c r="M2" t="n">
-        <v>1.39820636722879</v>
+        <v>0.09856125657661254</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2064492702701683</v>
+        <v>0.05640396151733591</v>
       </c>
       <c r="O2" t="n">
-        <v>0.08498705421537256</v>
+        <v>0.03152608089679527</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4614252999197991</v>
+        <v>0.4353656622096378</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.06400202764473212</v>
+        <v>-0.1495200746536932</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9722754614838974</v>
+        <v>1.004943824017964</v>
       </c>
       <c r="S2" t="n">
         <v>5000</v>
       </c>
       <c r="T2" t="n">
-        <v>1.688623307581887</v>
+        <v>1.483445301774754</v>
       </c>
       <c r="U2" t="n">
-        <v>48.51142280322171</v>
+        <v>35.96466015948098</v>
       </c>
       <c r="V2" t="n">
-        <v>0.09771068060853218</v>
+        <v>0.1466675369782948</v>
       </c>
       <c r="W2" t="n">
-        <v>0.09771068060853218</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.3455954647813743</v>
+        <v>0.3422242529493546</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>higher in SAD</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>higher in SAD</t>
+          <t>Neural_Dist_Safety_Background</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Neural_Dist_Safety_Background</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
         <is>
           <t>resolved</t>
         </is>
@@ -762,63 +747,60 @@
         <v>28</v>
       </c>
       <c r="K3" t="n">
-        <v>1.479823626483557</v>
+        <v>0.1285551021579494</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1942086984353445</v>
+        <v>0.09264756978923594</v>
       </c>
       <c r="M3" t="n">
-        <v>1.558473712815117</v>
+        <v>0.1267838346433344</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1195652140947562</v>
+        <v>0.09698240949272487</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.07865008633156001</v>
+        <v>0.001771267514614983</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4993130805700229</v>
+        <v>0.01863303336686996</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9740859627007233</v>
+        <v>-0.513565675083519</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02346077765077016</v>
+        <v>0.5922022128950996</v>
       </c>
       <c r="S3" t="n">
         <v>5000</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.696039382747858</v>
+        <v>0.06651606431530295</v>
       </c>
       <c r="U3" t="n">
-        <v>35.06238254286284</v>
+        <v>47.84413069520072</v>
       </c>
       <c r="V3" t="n">
-        <v>0.09874156136610693</v>
+        <v>0.9472441508466121</v>
       </c>
       <c r="W3" t="n">
-        <v>0.09874156136610693</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.3455954647813743</v>
+        <v>0.9472441508466121</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>higher in SAD</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>lower in SAD</t>
+          <t>Neural_Dist_Threat_Background</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Neural_Dist_Threat_Background</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
         <is>
           <t>resolved</t>
         </is>
@@ -871,63 +853,60 @@
         <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>1.517341694840898</v>
+        <v>0.1783705426639688</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1198274062129216</v>
+        <v>0.1269747265245408</v>
       </c>
       <c r="M4" t="n">
-        <v>1.519858740961526</v>
+        <v>0.1366094902291264</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1317298784074646</v>
+        <v>0.1171885142545761</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.00251704612062742</v>
+        <v>0.04176105243484235</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.01989374615125264</v>
+        <v>0.3432047005582242</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.6127509058360042</v>
+        <v>-0.1970101615398488</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5247360362081663</v>
+        <v>0.9713910618300602</v>
       </c>
       <c r="S4" t="n">
         <v>5000</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.07136347141985432</v>
+        <v>1.209854869467374</v>
       </c>
       <c r="U4" t="n">
-        <v>48.45301578991505</v>
+        <v>45.4332277238017</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9434022332141585</v>
+        <v>0.2325921056656618</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9434022332141585</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.9434022332141585</v>
+        <v>0.4070361849149082</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>higher in SAD</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>lower in SAD</t>
+          <t>Neural_Dist_Threat_Safety</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Neural_Dist_Threat_Safety</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
         <is>
           <t>resolved</t>
         </is>
@@ -949,17 +928,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Prototype_Certainty_CSS</t>
+          <t>Neural_Certainty_CSS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Prototype CSS certainty</t>
+          <t>CSS certainty</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2 * |P_prototype_safety_css - 0.50|</t>
+          <t>2 * |P(safety | CSS) - 0.50|</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -969,7 +948,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Higher = less ambiguous prototype safety evidence for CSS</t>
+          <t>Higher = less ambiguous CSS evidence</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -979,63 +958,60 @@
         <v>28</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1003852985579937</v>
+        <v>0.3831693613119109</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1198568282036435</v>
+        <v>0.2302050957355015</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1242159169597024</v>
+        <v>0.2367544285572005</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1134075112305132</v>
+        <v>0.1741286939539822</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.02383061840170872</v>
+        <v>0.1464149327547103</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.204823038800574</v>
+        <v>0.7275346571421177</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.8130648587471739</v>
+        <v>0.1569402358274535</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3631526495599417</v>
+        <v>1.472045034805979</v>
       </c>
       <c r="S5" t="n">
         <v>5000</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7238286201361032</v>
+        <v>2.515813511388849</v>
       </c>
       <c r="U5" t="n">
-        <v>45.98970210973896</v>
+        <v>40.28768443161758</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4728369475107381</v>
+        <v>0.01596119618209416</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4728369475107381</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.6619717265150333</v>
+        <v>0.1112580352005434</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>higher in SAD</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>lower in SAD</t>
+          <t>Neural_Certainty_CSS</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Prototype_Certainty_CSS</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
         <is>
           <t>resolved</t>
         </is>
@@ -1057,17 +1033,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Prototype_Certainty_CSR</t>
+          <t>Neural_Certainty_CSR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Prototype CSR certainty</t>
+          <t>CSR certainty</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2 * |P_prototype_threat_csr - 0.50|</t>
+          <t>2 * |P(threat | CSR) - 0.50|</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1077,7 +1053,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Higher = less ambiguous prototype threat evidence for CSR</t>
+          <t>Higher = less ambiguous CSR evidence</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -1087,63 +1063,60 @@
         <v>28</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6327387902661199</v>
+        <v>0.3310221787700166</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06126300121002913</v>
+        <v>0.2176137637339395</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6489889224798121</v>
+        <v>0.2090324688305265</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04549107177846967</v>
+        <v>0.1628462809179963</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0162501322136922</v>
+        <v>0.12198970993949</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.30571553273462</v>
+        <v>0.6440683005621686</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.8554525693680148</v>
+        <v>0.09126133778588713</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2614442466989809</v>
+        <v>1.317244525216265</v>
       </c>
       <c r="S6" t="n">
         <v>5000</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.055361038719713</v>
+        <v>2.224974947448372</v>
       </c>
       <c r="U6" t="n">
-        <v>39.79068672076174</v>
+        <v>39.99865565370761</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2976262368272386</v>
+        <v>0.03178801005729812</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2976262368272386</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.5814797502674219</v>
+        <v>0.1112580352005434</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>higher in SAD</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>lower in SAD</t>
+          <t>Neural_Certainty_CSR</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Prototype_Certainty_CSR</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
         <is>
           <t>resolved</t>
         </is>
@@ -1231,27 +1204,24 @@
         <v>0.9343969974782784</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9343969974782784</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.9434022332141585</v>
+        <v>0.9472441508466121</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>lower in SAD</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>lower in SAD</t>
+          <t>Neural_Safety_Trajectory_Slope</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Neural_Safety_Trajectory_Slope</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
         <is>
           <t>resolved</t>
         </is>
@@ -1339,27 +1309,24 @@
         <v>0.3322741430099554</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3322741430099554</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.5814797502674219</v>
+        <v>0.4651838002139375</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>lower in SAD</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>lower in SAD</t>
+          <t>Neural_Threat_Trajectory_Slope</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Neural_Threat_Trajectory_Slope</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
         <is>
           <t>resolved</t>
         </is>

--- a/code/Table_aim2_secondary.xlsx
+++ b/code/Table_aim2_secondary.xlsx
@@ -439,13 +439,13 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="21" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="22" customWidth="1" min="20" max="20"/>
     <col width="19" customWidth="1" min="21" max="21"/>
@@ -641,43 +641,43 @@
         <v>28</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1300873374734078</v>
+        <v>1.483193421444162</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08817329002033837</v>
+        <v>0.1524771781316907</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09856125657661254</v>
+        <v>1.39820636722879</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05640396151733591</v>
+        <v>0.2064492702701683</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03152608089679527</v>
+        <v>0.08498705421537256</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4353656622096378</v>
+        <v>0.4614252999197991</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1495200746536932</v>
+        <v>-0.06400202764473212</v>
       </c>
       <c r="R2" t="n">
-        <v>1.004943824017964</v>
+        <v>0.9722754614838974</v>
       </c>
       <c r="S2" t="n">
         <v>5000</v>
       </c>
       <c r="T2" t="n">
-        <v>1.483445301774754</v>
+        <v>1.688623307581887</v>
       </c>
       <c r="U2" t="n">
-        <v>35.96466015948098</v>
+        <v>48.51142280322171</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1466675369782948</v>
+        <v>0.09771068060853218</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3422242529493546</v>
+        <v>0.1727977323906871</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -747,47 +747,47 @@
         <v>28</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1285551021579494</v>
+        <v>1.479823626483557</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09264756978923594</v>
+        <v>0.1942086984353445</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1267838346433344</v>
+        <v>1.558473712815117</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09698240949272487</v>
+        <v>0.1195652140947562</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001771267514614983</v>
+        <v>-0.07865008633156001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01863303336686996</v>
+        <v>-0.4993130805700229</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.513565675083519</v>
+        <v>-0.9740859627007233</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5922022128950996</v>
+        <v>0.02346077765077016</v>
       </c>
       <c r="S3" t="n">
         <v>5000</v>
       </c>
       <c r="T3" t="n">
-        <v>0.06651606431530295</v>
+        <v>-1.696039382747858</v>
       </c>
       <c r="U3" t="n">
-        <v>47.84413069520072</v>
+        <v>35.06238254286284</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9472441508466121</v>
+        <v>0.09874156136610693</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9472441508466121</v>
+        <v>0.1727977323906871</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>higher in SAD</t>
+          <t>lower in SAD</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -853,47 +853,47 @@
         <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1783705426639688</v>
+        <v>1.517341694840898</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1269747265245408</v>
+        <v>0.1198274062129216</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1366094902291264</v>
+        <v>1.519858740961526</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1171885142545761</v>
+        <v>0.1317298784074646</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04176105243484235</v>
+        <v>-0.00251704612062742</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3432047005582242</v>
+        <v>-0.01989374615125264</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1970101615398488</v>
+        <v>-0.6127509058360042</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9713910618300602</v>
+        <v>0.5247360362081663</v>
       </c>
       <c r="S4" t="n">
         <v>5000</v>
       </c>
       <c r="T4" t="n">
-        <v>1.209854869467374</v>
+        <v>-0.07136347141985432</v>
       </c>
       <c r="U4" t="n">
-        <v>45.4332277238017</v>
+        <v>48.45301578991505</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2325921056656618</v>
+        <v>0.9434022332141585</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4070361849149082</v>
+        <v>0.9434022332141585</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>higher in SAD</t>
+          <t>lower in SAD</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1204,7 +1204,7 @@
         <v>0.9343969974782784</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9472441508466121</v>
+        <v>0.9434022332141585</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>

--- a/code/Table_aim2_secondary.xlsx
+++ b/code/Table_aim2_secondary.xlsx
@@ -439,13 +439,13 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="22" customWidth="1" min="20" max="20"/>
     <col width="19" customWidth="1" min="21" max="21"/>
@@ -641,43 +641,43 @@
         <v>28</v>
       </c>
       <c r="K2" t="n">
-        <v>1.483193421444162</v>
+        <v>0.1300873374734078</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1524771781316907</v>
+        <v>0.08817329002033837</v>
       </c>
       <c r="M2" t="n">
-        <v>1.39820636722879</v>
+        <v>0.09856125657661254</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2064492702701683</v>
+        <v>0.05640396151733591</v>
       </c>
       <c r="O2" t="n">
-        <v>0.08498705421537256</v>
+        <v>0.03152608089679527</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4614252999197991</v>
+        <v>0.4353656622096378</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.06400202764473212</v>
+        <v>-0.1495200746536932</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9722754614838974</v>
+        <v>1.004943824017964</v>
       </c>
       <c r="S2" t="n">
         <v>5000</v>
       </c>
       <c r="T2" t="n">
-        <v>1.688623307581887</v>
+        <v>1.483445301774754</v>
       </c>
       <c r="U2" t="n">
-        <v>48.51142280322171</v>
+        <v>35.96466015948098</v>
       </c>
       <c r="V2" t="n">
-        <v>0.09771068060853218</v>
+        <v>0.1466675369782948</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1727977323906871</v>
+        <v>0.3422242529493546</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -747,47 +747,47 @@
         <v>28</v>
       </c>
       <c r="K3" t="n">
-        <v>1.479823626483557</v>
+        <v>0.1285551021579494</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1942086984353445</v>
+        <v>0.09264756978923594</v>
       </c>
       <c r="M3" t="n">
-        <v>1.558473712815117</v>
+        <v>0.1267838346433344</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1195652140947562</v>
+        <v>0.09698240949272487</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.07865008633156001</v>
+        <v>0.001771267514614983</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4993130805700229</v>
+        <v>0.01863303336686996</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9740859627007233</v>
+        <v>-0.513565675083519</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02346077765077016</v>
+        <v>0.5922022128950996</v>
       </c>
       <c r="S3" t="n">
         <v>5000</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.696039382747858</v>
+        <v>0.06651606431530295</v>
       </c>
       <c r="U3" t="n">
-        <v>35.06238254286284</v>
+        <v>47.84413069520072</v>
       </c>
       <c r="V3" t="n">
-        <v>0.09874156136610693</v>
+        <v>0.9472441508466121</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1727977323906871</v>
+        <v>0.9472441508466121</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>lower in SAD</t>
+          <t>higher in SAD</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -853,47 +853,47 @@
         <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>1.517341694840898</v>
+        <v>0.1783705426639688</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1198274062129216</v>
+        <v>0.1269747265245408</v>
       </c>
       <c r="M4" t="n">
-        <v>1.519858740961526</v>
+        <v>0.1366094902291264</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1317298784074646</v>
+        <v>0.1171885142545761</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.00251704612062742</v>
+        <v>0.04176105243484235</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.01989374615125264</v>
+        <v>0.3432047005582242</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.6127509058360042</v>
+        <v>-0.1970101615398488</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5247360362081663</v>
+        <v>0.9713910618300602</v>
       </c>
       <c r="S4" t="n">
         <v>5000</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.07136347141985432</v>
+        <v>1.209854869467374</v>
       </c>
       <c r="U4" t="n">
-        <v>48.45301578991505</v>
+        <v>45.4332277238017</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9434022332141585</v>
+        <v>0.2325921056656618</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9434022332141585</v>
+        <v>0.4070361849149082</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>lower in SAD</t>
+          <t>higher in SAD</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1204,7 +1204,7 @@
         <v>0.9343969974782784</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9434022332141585</v>
+        <v>0.9472441508466121</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>

--- a/code/Table_aim2_secondary.xlsx
+++ b/code/Table_aim2_secondary.xlsx
@@ -439,7 +439,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
@@ -641,43 +641,43 @@
         <v>28</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1300873374734078</v>
+        <v>0.2314684506042999</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08817329002033837</v>
+        <v>0.1533706281069297</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09856125657661254</v>
+        <v>0.2074879754890014</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05640396151733591</v>
+        <v>0.1310787385108941</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03152608089679527</v>
+        <v>0.02398047511529852</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4353656622096378</v>
+        <v>0.1694465536944773</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1495200746536932</v>
+        <v>-0.3961783266510094</v>
       </c>
       <c r="R2" t="n">
-        <v>1.004943824017964</v>
+        <v>0.7290540536252698</v>
       </c>
       <c r="S2" t="n">
         <v>5000</v>
       </c>
       <c r="T2" t="n">
-        <v>1.483445301774754</v>
+        <v>0.5928157910303914</v>
       </c>
       <c r="U2" t="n">
-        <v>35.96466015948098</v>
+        <v>43.54635217281516</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1466675369782948</v>
+        <v>0.5563707173345738</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3422242529493546</v>
+        <v>0.6517481117828272</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -747,43 +747,43 @@
         <v>28</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1285551021579494</v>
+        <v>0.250406860425123</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09264756978923594</v>
+        <v>0.1177094810781026</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1267838346433344</v>
+        <v>0.2302064012448476</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09698240949272487</v>
+        <v>0.1267753928149779</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001771267514614983</v>
+        <v>0.02020045918027544</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01863303336686996</v>
+        <v>0.1645151819033414</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.513565675083519</v>
+        <v>-0.3872726190506065</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5922022128950996</v>
+        <v>0.7627129097762194</v>
       </c>
       <c r="S3" t="n">
         <v>5000</v>
       </c>
       <c r="T3" t="n">
-        <v>0.06651606431530295</v>
+        <v>0.5889536918794687</v>
       </c>
       <c r="U3" t="n">
-        <v>47.84413069520072</v>
+        <v>48.22395824619176</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9472441508466121</v>
+        <v>0.5586412386709947</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9472441508466121</v>
+        <v>0.6517481117828272</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -853,43 +853,43 @@
         <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1783705426639688</v>
+        <v>0.2991152799714809</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1269747265245408</v>
+        <v>0.1760392869776785</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1366094902291264</v>
+        <v>0.239382628137274</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1171885142545761</v>
+        <v>0.1424927437816819</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04176105243484235</v>
+        <v>0.05973265183420687</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3432047005582242</v>
+        <v>0.3770154856650065</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1970101615398488</v>
+        <v>-0.1819640990020789</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9713910618300602</v>
+        <v>0.9446261346784078</v>
       </c>
       <c r="S4" t="n">
         <v>5000</v>
       </c>
       <c r="T4" t="n">
-        <v>1.209854869467374</v>
+        <v>1.31208218114335</v>
       </c>
       <c r="U4" t="n">
-        <v>45.4332277238017</v>
+        <v>42.11345390330619</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2325921056656618</v>
+        <v>0.1965995474682463</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4070361849149082</v>
+        <v>0.4587322774259079</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>0.9343969974782784</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9472441508466121</v>
+        <v>0.9343969974782784</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>0.3322741430099554</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4651838002139375</v>
+        <v>0.5814797502674219</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
